--- a/outputs/q4/material_share.xlsx
+++ b/outputs/q4/material_share.xlsx
@@ -475,25 +475,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>49972.16388888888</v>
+        <v>38013.09654574172</v>
       </c>
       <c r="C2" t="n">
-        <v>27197.23333333333</v>
+        <v>18556.89398844614</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5442476614341796</v>
+        <v>0.4881710693080833</v>
       </c>
       <c r="E2" t="n">
-        <v>9028.166666666661</v>
+        <v>7328.058229120536</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1806639129484252</v>
+        <v>0.1927771977298028</v>
       </c>
       <c r="G2" t="n">
-        <v>13746.76388888889</v>
+        <v>12128.14432817504</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2750884256173951</v>
+        <v>0.3190517329621139</v>
       </c>
     </row>
     <row r="3">
@@ -501,25 +501,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>49972.1638888889</v>
+        <v>33935.14222399774</v>
       </c>
       <c r="C3" t="n">
-        <v>27197.23333333333</v>
+        <v>14731.34512489202</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4341029434223065</v>
       </c>
       <c r="E3" t="n">
-        <v>9028.166666666675</v>
+        <v>8144.220994985196</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.2399937192314429</v>
       </c>
       <c r="G3" t="n">
-        <v>13746.76388888889</v>
+        <v>11059.57610412053</v>
       </c>
       <c r="H3" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3259033373462506</v>
       </c>
     </row>
     <row r="4">
@@ -527,25 +527,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>49972.1638888889</v>
+        <v>36128.39316461299</v>
       </c>
       <c r="C4" t="n">
-        <v>27197.23333333333</v>
+        <v>15523.51200783277</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4296762365572829</v>
       </c>
       <c r="E4" t="n">
-        <v>9028.166666666675</v>
+        <v>8308.919564401513</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.2299830918730127</v>
       </c>
       <c r="G4" t="n">
-        <v>13746.76388888889</v>
+        <v>12295.96159237871</v>
       </c>
       <c r="H4" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3403406715697045</v>
       </c>
     </row>
     <row r="5">
@@ -553,25 +553,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>49972.1638888889</v>
+        <v>34539.20832448111</v>
       </c>
       <c r="C5" t="n">
-        <v>27197.23333333333</v>
+        <v>14976.56747965667</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4336106183719737</v>
       </c>
       <c r="E5" t="n">
-        <v>9028.166666666675</v>
+        <v>7720.884944315936</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.2235397196073957</v>
       </c>
       <c r="G5" t="n">
-        <v>13746.76388888889</v>
+        <v>11841.7559005085</v>
       </c>
       <c r="H5" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3428496620206306</v>
       </c>
     </row>
     <row r="6">
@@ -579,25 +579,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>49972.1638888889</v>
+        <v>35677.87033269257</v>
       </c>
       <c r="C6" t="n">
-        <v>27197.23333333333</v>
+        <v>15687.66492046722</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4397029523954574</v>
       </c>
       <c r="E6" t="n">
-        <v>9028.166666666675</v>
+        <v>8243.751666958444</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.231060643196645</v>
       </c>
       <c r="G6" t="n">
-        <v>13746.76388888889</v>
+        <v>11746.4537452669</v>
       </c>
       <c r="H6" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3292364044078976</v>
       </c>
     </row>
     <row r="7">
@@ -605,25 +605,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>49972.1638888889</v>
+        <v>36449.52301371008</v>
       </c>
       <c r="C7" t="n">
-        <v>27197.23333333333</v>
+        <v>15846.0102778222</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4347384812652255</v>
       </c>
       <c r="E7" t="n">
-        <v>9028.166666666675</v>
+        <v>8571.575064046063</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.2351628870649956</v>
       </c>
       <c r="G7" t="n">
-        <v>13746.76388888889</v>
+        <v>12031.93767184182</v>
       </c>
       <c r="H7" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3300986316697789</v>
       </c>
     </row>
     <row r="8">
@@ -631,25 +631,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>49972.1638888889</v>
+        <v>35426.43444461231</v>
       </c>
       <c r="C8" t="n">
-        <v>27197.23333333333</v>
+        <v>15966.74516786866</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4507014442232953</v>
       </c>
       <c r="E8" t="n">
-        <v>9028.166666666675</v>
+        <v>7775.97103967277</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.2194962931375485</v>
       </c>
       <c r="G8" t="n">
-        <v>13746.76388888889</v>
+        <v>11683.71823707088</v>
       </c>
       <c r="H8" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3298022626391562</v>
       </c>
     </row>
     <row r="9">
@@ -657,25 +657,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>49972.1638888889</v>
+        <v>35062.01246781861</v>
       </c>
       <c r="C9" t="n">
-        <v>27197.23333333333</v>
+        <v>15815.65041340328</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4510765155856226</v>
       </c>
       <c r="E9" t="n">
-        <v>9028.166666666675</v>
+        <v>7651.113368951343</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.2182166062479687</v>
       </c>
       <c r="G9" t="n">
-        <v>13746.76388888889</v>
+        <v>11595.24868546399</v>
       </c>
       <c r="H9" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3307068781664087</v>
       </c>
     </row>
     <row r="10">
@@ -683,25 +683,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.9600647084</v>
       </c>
       <c r="C10" t="n">
-        <v>27197.23333333333</v>
+        <v>16671.20381754767</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4675835107037505</v>
       </c>
       <c r="E10" t="n">
-        <v>9028.166666666675</v>
+        <v>6617.512827904879</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1856038660472708</v>
       </c>
       <c r="G10" t="n">
-        <v>13746.76388888889</v>
+        <v>12365.24341925584</v>
       </c>
       <c r="H10" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3468126232489786</v>
       </c>
     </row>
     <row r="11">
@@ -709,25 +709,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.9600647084</v>
       </c>
       <c r="C11" t="n">
-        <v>27197.23333333333</v>
+        <v>16537.69630858118</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4638389754901533</v>
       </c>
       <c r="E11" t="n">
-        <v>9028.166666666675</v>
+        <v>5895.441159623404</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1653516509505189</v>
       </c>
       <c r="G11" t="n">
-        <v>13746.76388888889</v>
+        <v>13220.82259650381</v>
       </c>
       <c r="H11" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3708093735593279</v>
       </c>
     </row>
     <row r="12">
@@ -735,25 +735,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C12" t="n">
-        <v>27197.23333333333</v>
+        <v>16829.92445876811</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4720352081009647</v>
       </c>
       <c r="E12" t="n">
-        <v>9028.166666666675</v>
+        <v>5393.266553323126</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1512669712855145</v>
       </c>
       <c r="G12" t="n">
-        <v>13746.76388888889</v>
+        <v>13430.76905261715</v>
       </c>
       <c r="H12" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3766978206135208</v>
       </c>
     </row>
     <row r="13">
@@ -761,25 +761,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C13" t="n">
-        <v>27197.23333333333</v>
+        <v>16616.33766597167</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4660446591574868</v>
       </c>
       <c r="E13" t="n">
-        <v>9028.166666666675</v>
+        <v>5923.790913213743</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1661467871300313</v>
       </c>
       <c r="G13" t="n">
-        <v>13746.76388888889</v>
+        <v>13113.83148552298</v>
       </c>
       <c r="H13" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3678085537124818</v>
       </c>
     </row>
     <row r="14">
@@ -787,25 +787,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C14" t="n">
-        <v>27197.23333333333</v>
+        <v>17462.60999532147</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4897803768116799</v>
       </c>
       <c r="E14" t="n">
-        <v>9028.166666666675</v>
+        <v>5270.516594680936</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1478241571235137</v>
       </c>
       <c r="G14" t="n">
-        <v>13746.76388888889</v>
+        <v>12920.83347470599</v>
       </c>
       <c r="H14" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3623954660648064</v>
       </c>
     </row>
     <row r="15">
@@ -813,25 +813,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C15" t="n">
-        <v>27197.23333333333</v>
+        <v>17327.70525626279</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4859966529612625</v>
       </c>
       <c r="E15" t="n">
-        <v>9028.166666666675</v>
+        <v>4788.212232409707</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1342967856507266</v>
       </c>
       <c r="G15" t="n">
-        <v>13746.76388888889</v>
+        <v>13538.04257603588</v>
       </c>
       <c r="H15" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3797065613880109</v>
       </c>
     </row>
     <row r="16">
@@ -839,25 +839,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.9600647084</v>
       </c>
       <c r="C16" t="n">
-        <v>27197.23333333333</v>
+        <v>17031.00068837289</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4776748685829937</v>
       </c>
       <c r="E16" t="n">
-        <v>9028.166666666675</v>
+        <v>5181.79301400651</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1453356935555565</v>
       </c>
       <c r="G16" t="n">
-        <v>13746.76388888889</v>
+        <v>13441.166362329</v>
       </c>
       <c r="H16" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3769894378614497</v>
       </c>
     </row>
     <row r="17">
@@ -865,25 +865,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C17" t="n">
-        <v>27197.23333333333</v>
+        <v>16200.31231431801</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4543762399721114</v>
       </c>
       <c r="E17" t="n">
-        <v>9028.166666666675</v>
+        <v>6518.072333301675</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1828148211719546</v>
       </c>
       <c r="G17" t="n">
-        <v>13746.76388888889</v>
+        <v>12935.57541708869</v>
       </c>
       <c r="H17" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3628089388559339</v>
       </c>
     </row>
     <row r="18">
@@ -891,25 +891,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C18" t="n">
-        <v>27197.23333333333</v>
+        <v>17020.67285260003</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4773851998967072</v>
       </c>
       <c r="E18" t="n">
-        <v>9028.166666666675</v>
+        <v>5993.964047333903</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1681149593609084</v>
       </c>
       <c r="G18" t="n">
-        <v>13746.76388888889</v>
+        <v>12639.32316477446</v>
       </c>
       <c r="H18" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3544998407423843</v>
       </c>
     </row>
     <row r="19">
@@ -917,25 +917,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.9600647084</v>
       </c>
       <c r="C19" t="n">
-        <v>27197.23333333333</v>
+        <v>19119.99856405579</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.5362657760696116</v>
       </c>
       <c r="E19" t="n">
-        <v>9028.166666666675</v>
+        <v>3707.533452858236</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1039865823075314</v>
       </c>
       <c r="G19" t="n">
-        <v>13746.76388888889</v>
+        <v>12826.42804779438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3597476416228571</v>
       </c>
     </row>
     <row r="20">
@@ -943,25 +943,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C20" t="n">
-        <v>27197.23333333333</v>
+        <v>18025.67737540137</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.5055729389578763</v>
       </c>
       <c r="E20" t="n">
-        <v>9028.166666666675</v>
+        <v>4866.509723853805</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1364928247807978</v>
       </c>
       <c r="G20" t="n">
-        <v>13746.76388888889</v>
+        <v>12761.77296545321</v>
       </c>
       <c r="H20" t="n">
-        <v>0.275088425617395</v>
+        <v>0.357934236261326</v>
       </c>
     </row>
     <row r="21">
@@ -969,25 +969,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C21" t="n">
-        <v>27197.23333333333</v>
+        <v>16898.63507398559</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4739623605152486</v>
       </c>
       <c r="E21" t="n">
-        <v>9028.166666666675</v>
+        <v>6544.023183987017</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.183542674421306</v>
       </c>
       <c r="G21" t="n">
-        <v>13746.76388888889</v>
+        <v>12211.30180673578</v>
       </c>
       <c r="H21" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3424949650634455</v>
       </c>
     </row>
     <row r="22">
@@ -995,25 +995,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C22" t="n">
-        <v>27197.23333333333</v>
+        <v>17967.73712725801</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.5039478670713815</v>
       </c>
       <c r="E22" t="n">
-        <v>9028.166666666675</v>
+        <v>4472.902022268154</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1254531618409367</v>
       </c>
       <c r="G22" t="n">
-        <v>13746.76388888889</v>
+        <v>13213.32091518223</v>
       </c>
       <c r="H22" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3705989710876819</v>
       </c>
     </row>
     <row r="23">
@@ -1021,25 +1021,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470842</v>
       </c>
       <c r="C23" t="n">
-        <v>27197.23333333333</v>
+        <v>17089.15705617504</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4793060020586749</v>
       </c>
       <c r="E23" t="n">
-        <v>9028.166666666675</v>
+        <v>5489.122991596292</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1539554927877317</v>
       </c>
       <c r="G23" t="n">
-        <v>13746.76388888889</v>
+        <v>13075.68001693708</v>
       </c>
       <c r="H23" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3667385051535933</v>
       </c>
     </row>
     <row r="24">
@@ -1047,25 +1047,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C24" t="n">
-        <v>27197.23333333333</v>
+        <v>17100.99082064877</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4796379080924582</v>
       </c>
       <c r="E24" t="n">
-        <v>9028.166666666675</v>
+        <v>6368.2239451943</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.1786119671878413</v>
       </c>
       <c r="G24" t="n">
-        <v>13746.76388888889</v>
+        <v>12184.74529886531</v>
       </c>
       <c r="H24" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3417501247197005</v>
       </c>
     </row>
     <row r="25">
@@ -1073,25 +1073,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>49972.1638888889</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C25" t="n">
-        <v>27197.23333333333</v>
+        <v>16549.46817807119</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5442476614341795</v>
+        <v>0.4641691455320965</v>
       </c>
       <c r="E25" t="n">
-        <v>9028.166666666675</v>
+        <v>7103.702292530106</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1806639129484255</v>
+        <v>0.199240204443983</v>
       </c>
       <c r="G25" t="n">
-        <v>13746.76388888889</v>
+        <v>12000.7895941071</v>
       </c>
       <c r="H25" t="n">
-        <v>0.275088425617395</v>
+        <v>0.3365906500239204</v>
       </c>
     </row>
   </sheetData>
